--- a/03_BOM/BEE-1012 PAY-EXP_V110_final.xlsx
+++ b/03_BOM/BEE-1012 PAY-EXP_V110_final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20398"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_Altium_Project\22_STL_EXP_v110\SpaceLiin-Satellite-4U-HW-1.1.0\03_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_AltiumProject\22_Satellite_EXP_V110\SpaceLiin-Satellite-4U-HW-1.1.0\03_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5B0B86-BF77-445F-9438-CD854A23B65A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADB9852-8D4C-40AA-9DF0-A420BF1BD846}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{FBB3F28C-C48D-4C37-853D-29F465BE6401}"/>
   </bookViews>
@@ -23,17 +23,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1487,18 +1476,18 @@
     <t>R38, R60, R144, R193, R194, R195, R196, R297, R300</t>
   </si>
   <si>
-    <t>R141, R192, R197, R198, R199, R200, R205, R206, R207, R208, R215, R216, R218, R219, R285, R296, R299, R304, R305, R329, R330, R347, R396, R397, R398, R399, R400, R401, R402, R449, R450, R451, R452, R454, R455, R463, R464, R466, R467, R468, R469, R489, R490, R501, R504, R526, R530, R633, R634, R638, R639</t>
+    <t>R141, R192, R197, R198, R199, R200, R205, R206, R207, R208, R215, R216, R218, R219, R285, R296, R299, R304, R305, R329, R330, R347, R396, R397, R398, R399, R400, R401, R402, R449, R450, R451, R452, R454, R455, R463, R464, R466, R467, R468, R469, R489, R490, R501, R504, R526, R530, R633, R634, R638, R639, R657, R658</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1927,18 +1916,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031DED2F-9990-4F66-BB78-0D4129BA0905}">
   <dimension ref="A1:H135"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.21875" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" customWidth="1"/>
-    <col min="3" max="3" width="29.77734375" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26.44140625" customWidth="1"/>
-    <col min="7" max="7" width="44.21875" customWidth="1"/>
+    <col min="1" max="1" width="20.19921875" customWidth="1"/>
+    <col min="2" max="2" width="28.09765625" customWidth="1"/>
+    <col min="3" max="3" width="29.796875" customWidth="1"/>
+    <col min="4" max="4" width="7.8984375" customWidth="1"/>
+    <col min="5" max="5" width="16.296875" customWidth="1"/>
+    <col min="6" max="6" width="26.3984375" customWidth="1"/>
+    <col min="7" max="7" width="44.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="4" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1961,7 +1950,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
         <v>133</v>
       </c>
@@ -1984,7 +1973,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>107</v>
       </c>
@@ -2007,7 +1996,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>77</v>
       </c>
@@ -2030,7 +2019,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>30</v>
       </c>
@@ -2053,7 +2042,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -2076,7 +2065,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
         <v>67</v>
       </c>
@@ -2099,7 +2088,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
         <v>100</v>
       </c>
@@ -2122,7 +2111,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
         <v>82</v>
       </c>
@@ -2145,7 +2134,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
         <v>125</v>
       </c>
@@ -2168,7 +2157,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
@@ -2191,7 +2180,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
         <v>88</v>
       </c>
@@ -2214,7 +2203,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
         <v>96</v>
       </c>
@@ -2237,7 +2226,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
         <v>100</v>
       </c>
@@ -2260,7 +2249,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
         <v>60</v>
       </c>
@@ -2283,7 +2272,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
         <v>51</v>
       </c>
@@ -2306,7 +2295,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
         <v>35</v>
       </c>
@@ -2329,7 +2318,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18" s="2" t="s">
         <v>105</v>
       </c>
@@ -2352,7 +2341,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19" s="2" t="s">
         <v>67</v>
       </c>
@@ -2375,7 +2364,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20" s="2" t="s">
         <v>58</v>
       </c>
@@ -2398,7 +2387,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
@@ -2421,7 +2410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22" s="2" t="s">
         <v>67</v>
       </c>
@@ -2444,7 +2433,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8">
       <c r="A23" s="2" t="s">
         <v>319</v>
       </c>
@@ -2467,7 +2456,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24" s="2" t="s">
         <v>47</v>
       </c>
@@ -2493,7 +2482,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
@@ -2516,7 +2505,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26" s="2" t="s">
         <v>319</v>
       </c>
@@ -2539,7 +2528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27" s="2" t="s">
         <v>337</v>
       </c>
@@ -2562,7 +2551,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28" s="2" t="s">
         <v>17</v>
       </c>
@@ -2585,7 +2574,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
@@ -2608,7 +2597,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
@@ -2631,7 +2620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31" s="2" t="s">
         <v>15</v>
       </c>
@@ -2654,7 +2643,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
         <v>249</v>
       </c>
@@ -2677,7 +2666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33" s="2" t="s">
         <v>183</v>
       </c>
@@ -2700,7 +2689,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" s="10" t="s">
         <v>266</v>
       </c>
@@ -2723,7 +2712,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" s="2" t="s">
         <v>168</v>
       </c>
@@ -2746,7 +2735,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36" s="2" t="s">
         <v>150</v>
       </c>
@@ -2769,7 +2758,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37" s="2" t="s">
         <v>144</v>
       </c>
@@ -2792,7 +2781,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38" s="2" t="s">
         <v>159</v>
       </c>
@@ -2815,7 +2804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" s="2" t="s">
         <v>165</v>
       </c>
@@ -2838,7 +2827,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40" s="2" t="s">
         <v>171</v>
       </c>
@@ -2859,7 +2848,7 @@
       </c>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" s="2" t="s">
         <v>153</v>
       </c>
@@ -2882,7 +2871,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42" s="2" t="s">
         <v>156</v>
       </c>
@@ -2905,7 +2894,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43" s="2" t="s">
         <v>139</v>
       </c>
@@ -2926,7 +2915,7 @@
       </c>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44" s="2" t="s">
         <v>139</v>
       </c>
@@ -2949,7 +2938,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45" s="10" t="s">
         <v>237</v>
       </c>
@@ -2972,7 +2961,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46" s="2" t="s">
         <v>162</v>
       </c>
@@ -2995,7 +2984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
         <v>136</v>
       </c>
@@ -3018,7 +3007,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" s="2" t="s">
         <v>147</v>
       </c>
@@ -3041,7 +3030,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49" s="10" t="s">
         <v>210</v>
       </c>
@@ -3064,7 +3053,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" s="10" t="s">
         <v>210</v>
       </c>
@@ -3087,7 +3076,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7">
       <c r="A51" s="10" t="s">
         <v>7</v>
       </c>
@@ -3110,7 +3099,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" s="2" t="s">
         <v>316</v>
       </c>
@@ -3133,7 +3122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" s="2" t="s">
         <v>110</v>
       </c>
@@ -3154,7 +3143,7 @@
       </c>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7">
       <c r="A54" s="2" t="s">
         <v>53</v>
       </c>
@@ -3177,7 +3166,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7">
       <c r="A55" s="2" t="s">
         <v>205</v>
       </c>
@@ -3200,7 +3189,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="A56" s="2" t="s">
         <v>208</v>
       </c>
@@ -3223,7 +3212,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" s="2" t="s">
         <v>189</v>
       </c>
@@ -3246,7 +3235,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" s="2" t="s">
         <v>177</v>
       </c>
@@ -3269,7 +3258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7">
       <c r="A59" s="2" t="s">
         <v>131</v>
       </c>
@@ -3292,7 +3281,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
         <v>62</v>
       </c>
@@ -3315,7 +3304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7">
       <c r="A61" s="2" t="s">
         <v>42</v>
       </c>
@@ -3336,7 +3325,7 @@
       </c>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="A62" s="2" t="s">
         <v>98</v>
       </c>
@@ -3359,7 +3348,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7">
       <c r="A63" s="2" t="s">
         <v>72</v>
       </c>
@@ -3380,7 +3369,7 @@
       </c>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7">
       <c r="A64" s="2" t="s">
         <v>119</v>
       </c>
@@ -3403,7 +3392,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7">
       <c r="A65" s="10" t="s">
         <v>218</v>
       </c>
@@ -3426,7 +3415,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7">
       <c r="A66" s="10" t="s">
         <v>210</v>
       </c>
@@ -3449,7 +3438,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7">
       <c r="A67" s="10" t="s">
         <v>217</v>
       </c>
@@ -3472,7 +3461,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7">
       <c r="A68" s="2" t="s">
         <v>121</v>
       </c>
@@ -3495,7 +3484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7">
       <c r="A69" s="2" t="s">
         <v>103</v>
       </c>
@@ -3518,7 +3507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7">
       <c r="A70" s="2" t="s">
         <v>123</v>
       </c>
@@ -3541,7 +3530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7">
       <c r="A71" s="10" t="s">
         <v>215</v>
       </c>
@@ -3564,7 +3553,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7">
       <c r="A72" s="2" t="s">
         <v>127</v>
       </c>
@@ -3587,7 +3576,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7">
       <c r="A73" s="10" t="s">
         <v>218</v>
       </c>
@@ -3610,7 +3599,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7">
       <c r="A74" s="2" t="s">
         <v>86</v>
       </c>
@@ -3633,7 +3622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7">
       <c r="A75" s="2" t="s">
         <v>90</v>
       </c>
@@ -3656,7 +3645,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7">
       <c r="A76" s="2" t="s">
         <v>90</v>
       </c>
@@ -3677,7 +3666,7 @@
       </c>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7">
       <c r="A77" s="2" t="s">
         <v>64</v>
       </c>
@@ -3698,7 +3687,7 @@
       </c>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7">
       <c r="A78" s="2" t="s">
         <v>19</v>
       </c>
@@ -3721,7 +3710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7">
       <c r="A79" s="2" t="s">
         <v>251</v>
       </c>
@@ -3744,7 +3733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7">
       <c r="A80" s="2" t="s">
         <v>66</v>
       </c>
@@ -3755,7 +3744,7 @@
         <v>21</v>
       </c>
       <c r="D80" s="1">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>405</v>
@@ -3767,7 +3756,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8">
       <c r="A81" s="2" t="s">
         <v>74</v>
       </c>
@@ -3790,7 +3779,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8">
       <c r="A82" s="2" t="s">
         <v>84</v>
       </c>
@@ -3811,7 +3800,7 @@
       </c>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8">
       <c r="A83" s="2" t="s">
         <v>114</v>
       </c>
@@ -3834,7 +3823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8">
       <c r="A84" s="2" t="s">
         <v>129</v>
       </c>
@@ -3857,7 +3846,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8">
       <c r="A85" s="2" t="s">
         <v>116</v>
       </c>
@@ -3880,7 +3869,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8">
       <c r="A86" s="2" t="s">
         <v>37</v>
       </c>
@@ -3903,7 +3892,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8">
       <c r="A87" s="2" t="s">
         <v>56</v>
       </c>
@@ -3926,7 +3915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8">
       <c r="A88" s="2" t="s">
         <v>80</v>
       </c>
@@ -3949,7 +3938,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8">
       <c r="A89" s="2" t="s">
         <v>19</v>
       </c>
@@ -3972,7 +3961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8">
       <c r="A90" s="2" t="s">
         <v>27</v>
       </c>
@@ -3995,7 +3984,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8">
       <c r="A91" s="2" t="s">
         <v>37</v>
       </c>
@@ -4018,7 +4007,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8">
       <c r="A92" s="2" t="s">
         <v>74</v>
       </c>
@@ -4041,7 +4030,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8">
       <c r="A93" s="2" t="s">
         <v>37</v>
       </c>
@@ -4062,7 +4051,7 @@
       </c>
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8">
       <c r="A94" s="10" t="s">
         <v>221</v>
       </c>
@@ -4085,7 +4074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8">
       <c r="A95" s="2" t="s">
         <v>93</v>
       </c>
@@ -4111,7 +4100,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -4129,7 +4118,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7">
       <c r="A97" s="2" t="s">
         <v>116</v>
       </c>
@@ -4152,7 +4141,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7">
       <c r="A98" s="2" t="s">
         <v>331</v>
       </c>
@@ -4173,7 +4162,7 @@
       </c>
       <c r="G98" s="1"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7">
       <c r="A99" s="2" t="s">
         <v>292</v>
       </c>
@@ -4194,7 +4183,7 @@
       </c>
       <c r="G99" s="1"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7">
       <c r="A100" s="2" t="s">
         <v>290</v>
       </c>
@@ -4215,7 +4204,7 @@
       </c>
       <c r="G100" s="1"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7">
       <c r="A101" s="2" t="s">
         <v>323</v>
       </c>
@@ -4236,7 +4225,7 @@
       </c>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7">
       <c r="A102" s="2" t="s">
         <v>284</v>
       </c>
@@ -4253,7 +4242,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7">
       <c r="A103" s="2" t="s">
         <v>296</v>
       </c>
@@ -4274,7 +4263,7 @@
       </c>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7">
       <c r="A104" s="2" t="s">
         <v>328</v>
       </c>
@@ -4295,7 +4284,7 @@
       </c>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7">
       <c r="A105" s="2" t="s">
         <v>240</v>
       </c>
@@ -4316,7 +4305,7 @@
       </c>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7">
       <c r="A106" s="2" t="s">
         <v>287</v>
       </c>
@@ -4337,7 +4326,7 @@
       </c>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7">
       <c r="A107" s="2" t="s">
         <v>192</v>
       </c>
@@ -4358,7 +4347,7 @@
       </c>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7">
       <c r="A108" s="2" t="s">
         <v>174</v>
       </c>
@@ -4379,7 +4368,7 @@
       </c>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7">
       <c r="A109" s="2" t="s">
         <v>302</v>
       </c>
@@ -4400,7 +4389,7 @@
       </c>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7">
       <c r="A110" s="2" t="s">
         <v>307</v>
       </c>
@@ -4421,7 +4410,7 @@
       </c>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7">
       <c r="A111" s="2" t="s">
         <v>180</v>
       </c>
@@ -4442,7 +4431,7 @@
       </c>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7">
       <c r="A112" s="2" t="s">
         <v>299</v>
       </c>
@@ -4463,7 +4452,7 @@
       </c>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7">
       <c r="A113" s="2" t="s">
         <v>325</v>
       </c>
@@ -4484,7 +4473,7 @@
       </c>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7">
       <c r="A114" s="2" t="s">
         <v>310</v>
       </c>
@@ -4505,7 +4494,7 @@
       </c>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7">
       <c r="A115" s="2" t="s">
         <v>334</v>
       </c>
@@ -4526,7 +4515,7 @@
       </c>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7">
       <c r="A116" s="6" t="s">
         <v>223</v>
       </c>
@@ -4547,7 +4536,7 @@
       </c>
       <c r="G116" s="7"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7">
       <c r="A117" s="2" t="s">
         <v>257</v>
       </c>
@@ -4568,7 +4557,7 @@
       </c>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7">
       <c r="A118" s="2" t="s">
         <v>282</v>
       </c>
@@ -4589,7 +4578,7 @@
       </c>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7">
       <c r="A119" s="2" t="s">
         <v>272</v>
       </c>
@@ -4610,7 +4599,7 @@
       </c>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7">
       <c r="A120" s="2" t="s">
         <v>278</v>
       </c>
@@ -4631,7 +4620,7 @@
       </c>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7">
       <c r="A121" s="2" t="s">
         <v>243</v>
       </c>
@@ -4652,7 +4641,7 @@
       </c>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7">
       <c r="A122" s="2" t="s">
         <v>263</v>
       </c>
@@ -4673,7 +4662,7 @@
       </c>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7">
       <c r="A123" s="2" t="s">
         <v>275</v>
       </c>
@@ -4694,7 +4683,7 @@
       </c>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7">
       <c r="A124" s="2" t="s">
         <v>269</v>
       </c>
@@ -4715,7 +4704,7 @@
       </c>
       <c r="G124" s="1"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
         <v>260</v>
       </c>
@@ -4736,7 +4725,7 @@
       </c>
       <c r="G125" s="1"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7">
       <c r="A126" s="2" t="s">
         <v>186</v>
       </c>
@@ -4757,7 +4746,7 @@
       </c>
       <c r="G126" s="1"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7">
       <c r="A127" s="2" t="s">
         <v>313</v>
       </c>
@@ -4778,7 +4767,7 @@
       </c>
       <c r="G127" s="1"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7">
       <c r="A128" s="2" t="s">
         <v>246</v>
       </c>
@@ -4799,7 +4788,7 @@
       </c>
       <c r="G128" s="1"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7">
       <c r="A129" s="2" t="s">
         <v>254</v>
       </c>
@@ -4820,7 +4809,7 @@
       </c>
       <c r="G129" s="1"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7">
       <c r="A130" s="2" t="s">
         <v>234</v>
       </c>
@@ -4841,7 +4830,7 @@
       </c>
       <c r="G130" s="1"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7">
       <c r="A131" s="2" t="s">
         <v>195</v>
       </c>
@@ -4862,7 +4851,7 @@
       </c>
       <c r="G131" s="1"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7">
       <c r="A132" s="6" t="s">
         <v>225</v>
       </c>
@@ -4883,7 +4872,7 @@
       </c>
       <c r="G132" s="7"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7">
       <c r="A133" s="2" t="s">
         <v>200</v>
       </c>
@@ -4904,7 +4893,7 @@
       </c>
       <c r="G133" s="1"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7">
       <c r="A134" s="6" t="s">
         <v>230</v>
       </c>
@@ -4925,7 +4914,7 @@
       </c>
       <c r="G134" s="7"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7">
       <c r="A135" s="2" t="s">
         <v>200</v>
       </c>
@@ -4949,7 +4938,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G135">
+  <sortState ref="A2:G135">
     <sortCondition ref="B2:B135"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
